--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/MISSOURI_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/MISSOURI_2017.xlsx
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C221">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C537">
